--- a/lca/results/lca_results_glo.xlsx
+++ b/lca/results/lca_results_glo.xlsx
@@ -405,7 +405,7 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>8.250608917980566</v>
+        <v>3.133773539162445</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -413,7 +413,7 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>4.639562766917133</v>
+        <v>1.361055930104192</v>
       </c>
     </row>
     <row r="4" spans="1:2">
